--- a/BICICLETERO 2026.xlsx
+++ b/BICICLETERO 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\BICICLETERO\ConceptoStyle\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Concepto Style\Desktop\BICICLETERO 2.0\bicicletero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2EB1ED-FD91-47E0-B23D-F6CBF6FD4086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FF9420-D6E1-488D-93B8-90DB8895628B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2325" yWindow="825" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="212">
   <si>
     <t>ESPACIO</t>
   </si>
@@ -593,6 +593,75 @@
   </si>
   <si>
     <t>se mudo</t>
+  </si>
+  <si>
+    <t>1.jpeg</t>
+  </si>
+  <si>
+    <t>2.jpeg</t>
+  </si>
+  <si>
+    <t>3.jpeg</t>
+  </si>
+  <si>
+    <t>4.jpeg</t>
+  </si>
+  <si>
+    <t>5.jpeg</t>
+  </si>
+  <si>
+    <t>6.jpeg</t>
+  </si>
+  <si>
+    <t>7.jpeg</t>
+  </si>
+  <si>
+    <t>8.jpeg</t>
+  </si>
+  <si>
+    <t>9.jpeg</t>
+  </si>
+  <si>
+    <t>10.jpeg</t>
+  </si>
+  <si>
+    <t>11.jpeg</t>
+  </si>
+  <si>
+    <t>12.jpeg</t>
+  </si>
+  <si>
+    <t>13.jpeg</t>
+  </si>
+  <si>
+    <t>14.jpeg</t>
+  </si>
+  <si>
+    <t>15.jpeg</t>
+  </si>
+  <si>
+    <t>16.jpeg</t>
+  </si>
+  <si>
+    <t>17.jpeg</t>
+  </si>
+  <si>
+    <t>18.jpeg</t>
+  </si>
+  <si>
+    <t>19.jpeg</t>
+  </si>
+  <si>
+    <t>20.jpeg</t>
+  </si>
+  <si>
+    <t>21.jpeg</t>
+  </si>
+  <si>
+    <t>23.jpeg</t>
+  </si>
+  <si>
+    <t>77.jpeg</t>
   </si>
 </sst>
 </file>
@@ -838,22 +907,6 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
@@ -877,13 +930,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Hoja 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1118,7 +1187,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -1176,7 +1245,9 @@
       <c r="G2" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H2" s="5"/>
+      <c r="H2" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
     </row>
@@ -1194,7 +1265,9 @@
       <c r="G3" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H3" s="5"/>
+      <c r="H3" s="6" t="s">
+        <v>190</v>
+      </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
     </row>
@@ -1212,7 +1285,9 @@
       <c r="G4" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="6" t="s">
+        <v>191</v>
+      </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
     </row>
@@ -1230,7 +1305,9 @@
       <c r="G5" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="6" t="s">
+        <v>192</v>
+      </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
     </row>
@@ -1248,7 +1325,9 @@
       <c r="G6" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="6" t="s">
+        <v>193</v>
+      </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
@@ -1266,7 +1345,9 @@
       <c r="G7" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="6" t="s">
+        <v>194</v>
+      </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
@@ -1284,7 +1365,9 @@
       <c r="G8" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="6" t="s">
+        <v>195</v>
+      </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
     </row>
@@ -1302,7 +1385,9 @@
       <c r="G9" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="6" t="s">
+        <v>196</v>
+      </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
     </row>
@@ -1320,7 +1405,9 @@
       <c r="G10" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="6" t="s">
+        <v>197</v>
+      </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
     </row>
@@ -1338,7 +1425,9 @@
       <c r="G11" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="6" t="s">
+        <v>198</v>
+      </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
     </row>
@@ -1356,7 +1445,9 @@
       <c r="G12" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="6" t="s">
+        <v>199</v>
+      </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
     </row>
@@ -1374,7 +1465,9 @@
       <c r="G13" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H13" s="5"/>
+      <c r="H13" s="6" t="s">
+        <v>200</v>
+      </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
@@ -1392,7 +1485,9 @@
       <c r="G14" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="6" t="s">
+        <v>201</v>
+      </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
     </row>
@@ -1410,7 +1505,9 @@
       <c r="G15" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="6" t="s">
+        <v>202</v>
+      </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
     </row>
@@ -1428,7 +1525,9 @@
       <c r="G16" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="6" t="s">
+        <v>203</v>
+      </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
     </row>
@@ -1446,7 +1545,9 @@
       <c r="G17" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H17" s="5"/>
+      <c r="H17" s="6" t="s">
+        <v>204</v>
+      </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
     </row>
@@ -1464,7 +1565,9 @@
       <c r="G18" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="H18" s="6" t="s">
+        <v>205</v>
+      </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
     </row>
@@ -1482,7 +1585,9 @@
       <c r="G19" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="6" t="s">
+        <v>206</v>
+      </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
     </row>
@@ -1500,7 +1605,9 @@
       <c r="G20" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="6" t="s">
+        <v>207</v>
+      </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
     </row>
@@ -1518,7 +1625,9 @@
       <c r="G21" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="5"/>
+      <c r="H21" s="6" t="s">
+        <v>208</v>
+      </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
     </row>
@@ -1536,7 +1645,9 @@
       <c r="G22" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H22" s="5"/>
+      <c r="H22" s="6" t="s">
+        <v>209</v>
+      </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
     </row>
@@ -1578,7 +1689,9 @@
       <c r="G24" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="5"/>
+      <c r="H24" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
     </row>
@@ -3038,7 +3151,9 @@
       <c r="G79" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H79" s="5"/>
+      <c r="H79" s="6" t="s">
+        <v>211</v>
+      </c>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
     </row>
@@ -3156,7 +3271,7 @@
   <customSheetViews>
     <customSheetView guid="{77038CD4-2297-4E69-A928-9CF498AA6CA5}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:J83" xr:uid="{107E50ED-EB0B-4F62-A6F5-D7DE6CEE1B54}"/>
+      <autoFilter ref="A1:J83" xr:uid="{1C586E98-7F26-4B30-BA7A-136B29AF2F17}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations count="1">
@@ -3224,12 +3339,13 @@
     <hyperlink ref="H81" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
     <hyperlink ref="H82" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
     <hyperlink ref="H83" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="H2" r:id="rId60" display="22.jpeg" xr:uid="{CB170EA3-56E5-49B0-BE90-CB48DE40BD7E}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
   <tableParts count="1">
-    <tablePart r:id="rId60"/>
+    <tablePart r:id="rId61"/>
   </tableParts>
 </worksheet>
 </file>
--- a/BICICLETERO 2026.xlsx
+++ b/BICICLETERO 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Concepto Style\Desktop\BICICLETERO 2.0\bicicletero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FF9420-D6E1-488D-93B8-90DB8895628B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A120C5DC-DF79-4363-B751-3104BF0EADEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="825" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3600" yWindow="105" windowWidth="15375" windowHeight="10185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="209">
   <si>
     <t>ESPACIO</t>
   </si>
@@ -352,9 +352,6 @@
     <t>BRAULIO ALIAGA</t>
   </si>
   <si>
-    <t>BIANCHI/CON SILLA DE NIÑO</t>
-  </si>
-  <si>
     <t>49.jpeg</t>
   </si>
   <si>
@@ -409,12 +406,6 @@
     <t>THALIA SANCHEZ</t>
   </si>
   <si>
-    <t xml:space="preserve">BIANCHI  </t>
-  </si>
-  <si>
-    <t>GRIS/NEGRO/ROJO</t>
-  </si>
-  <si>
     <t>55.jpeg</t>
   </si>
   <si>
@@ -463,9 +454,6 @@
     <t>HERNAN GOMEZ</t>
   </si>
   <si>
-    <t>TREEK 3700</t>
-  </si>
-  <si>
     <t>61.jpeg</t>
   </si>
   <si>
@@ -662,6 +650,9 @@
   </si>
   <si>
     <t>77.jpeg</t>
+  </si>
+  <si>
+    <t>TREK 3700</t>
   </si>
 </sst>
 </file>
@@ -839,7 +830,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -900,6 +891,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1246,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
@@ -1266,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -1286,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -1306,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -1326,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
@@ -1346,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
@@ -1366,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
@@ -1386,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
@@ -1406,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -1426,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -1446,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -1466,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
@@ -1486,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
@@ -1506,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
@@ -1526,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
@@ -1546,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
@@ -1566,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
@@ -1586,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
@@ -1606,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
@@ -1626,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
@@ -1646,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
@@ -1690,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
@@ -2424,23 +2418,13 @@
       <c r="B51" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="3">
-        <v>514</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G51" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
@@ -2456,10 +2440,10 @@
         <v>312</v>
       </c>
       <c r="D52" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>22</v>
@@ -2468,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
@@ -2484,19 +2468,19 @@
         <v>608</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="F53" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="G53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="G53" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
@@ -2512,10 +2496,10 @@
         <v>408</v>
       </c>
       <c r="D54" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>22</v>
@@ -2524,7 +2508,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
@@ -2542,13 +2526,13 @@
         <v>84</v>
       </c>
       <c r="F55" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="G55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
@@ -2564,19 +2548,19 @@
         <v>505</v>
       </c>
       <c r="D56" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="F56" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="G56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="G56" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
@@ -2588,23 +2572,17 @@
       <c r="B57" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C57" s="16">
-        <v>708</v>
-      </c>
+      <c r="C57" s="21"/>
       <c r="D57" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G57" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
@@ -2620,19 +2598,19 @@
         <v>320</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G58" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
@@ -2651,16 +2629,16 @@
         <v>32</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G59" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
@@ -2672,8 +2650,12 @@
       <c r="B60" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C60" s="17"/>
-      <c r="D60" s="3"/>
+      <c r="C60" s="3">
+        <v>514</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="E60" s="3" t="s">
         <v>51</v>
       </c>
@@ -2681,10 +2663,10 @@
         <v>48</v>
       </c>
       <c r="G60" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
@@ -2700,19 +2682,19 @@
         <v>204</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G61" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
@@ -2728,19 +2710,19 @@
         <v>207</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G62" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G62" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>143</v>
       </c>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
@@ -2756,10 +2738,10 @@
         <v>418</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>14</v>
@@ -2768,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
@@ -2784,10 +2766,10 @@
         <v>506</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>33</v>
@@ -2796,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
@@ -2816,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
@@ -2832,19 +2814,19 @@
         <v>505</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G66" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
@@ -2860,19 +2842,19 @@
         <v>713</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E67" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="G67" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
@@ -2888,7 +2870,7 @@
         <v>216</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>65</v>
@@ -2900,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
@@ -2916,19 +2898,19 @@
         <v>517</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G69" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
@@ -2948,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
@@ -2968,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
@@ -2986,13 +2968,13 @@
         <v>65</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G72" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
@@ -3008,19 +2990,19 @@
         <v>309</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G73" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
@@ -3040,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
@@ -3060,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
@@ -3080,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
@@ -3100,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
@@ -3115,16 +3097,16 @@
       <c r="C78" s="17"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G78" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
@@ -3140,10 +3122,10 @@
         <v>620</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>33</v>
@@ -3152,7 +3134,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
@@ -3162,16 +3144,16 @@
         <v>78</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C80" s="3">
         <v>506</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>22</v>
@@ -3180,7 +3162,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
@@ -3190,13 +3172,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C81" s="3">
         <v>414</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>29</v>
@@ -3208,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
@@ -3218,25 +3200,25 @@
         <v>80</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C82" s="3">
         <v>413</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G82" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
@@ -3246,24 +3228,24 @@
         <v>81</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C83" s="17"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G83" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J83" s="5"/>
     </row>
@@ -3271,7 +3253,7 @@
   <customSheetViews>
     <customSheetView guid="{77038CD4-2297-4E69-A928-9CF498AA6CA5}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:J83" xr:uid="{1C586E98-7F26-4B30-BA7A-136B29AF2F17}"/>
+      <autoFilter ref="A1:J83" xr:uid="{51EB7776-0972-4E67-9267-1849D967912E}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations count="1">

--- a/BICICLETERO 2026.xlsx
+++ b/BICICLETERO 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Concepto Style\Desktop\BICICLETERO 2.0\bicicletero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A120C5DC-DF79-4363-B751-3104BF0EADEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB26690-6F8F-41B4-BB93-FC0B101D6EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3600" yWindow="105" windowWidth="15375" windowHeight="10185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="208">
   <si>
     <t>ESPACIO</t>
   </si>
@@ -401,9 +401,6 @@
   </si>
   <si>
     <t>54.jpeg</t>
-  </si>
-  <si>
-    <t>THALIA SANCHEZ</t>
   </si>
   <si>
     <t>55.jpeg</t>
@@ -830,7 +827,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -891,9 +888,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1240,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
@@ -1260,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -1280,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -1300,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -1320,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
@@ -1340,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
@@ -1360,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
@@ -1380,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
@@ -1400,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -1420,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -1440,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -1460,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
@@ -1480,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
@@ -1500,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
@@ -1520,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
@@ -1540,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
@@ -1560,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
@@ -1580,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
@@ -1600,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
@@ -1620,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
@@ -1640,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
@@ -1684,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
@@ -2572,17 +2566,15 @@
       <c r="B57" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C57" s="21"/>
-      <c r="D57" s="3" t="s">
-        <v>125</v>
-      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
@@ -2598,19 +2590,19 @@
         <v>320</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F58" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="G58" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
@@ -2629,16 +2621,16 @@
         <v>32</v>
       </c>
       <c r="E59" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="G59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H59" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="G59" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
@@ -2666,7 +2658,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
@@ -2682,10 +2674,10 @@
         <v>204</v>
       </c>
       <c r="D61" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>123</v>
@@ -2694,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
@@ -2710,19 +2702,19 @@
         <v>207</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="F62" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="G62" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="G62" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
@@ -2738,10 +2730,10 @@
         <v>418</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>14</v>
@@ -2750,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
@@ -2766,10 +2758,10 @@
         <v>506</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>33</v>
@@ -2778,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
@@ -2798,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
@@ -2817,7 +2809,7 @@
         <v>121</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>123</v>
@@ -2826,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
@@ -2842,7 +2834,7 @@
         <v>713</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>122</v>
@@ -2854,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
@@ -2870,7 +2862,7 @@
         <v>216</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>65</v>
@@ -2882,7 +2874,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
@@ -2898,19 +2890,19 @@
         <v>517</v>
       </c>
       <c r="D69" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="F69" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="G69" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H69" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="G69" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H69" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
@@ -2930,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
@@ -2950,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
@@ -2968,13 +2960,13 @@
         <v>65</v>
       </c>
       <c r="F72" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="G72" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
@@ -2990,19 +2982,19 @@
         <v>309</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F73" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G73" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="G73" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H73" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
@@ -3022,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
@@ -3042,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
@@ -3062,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
@@ -3082,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
@@ -3097,7 +3089,7 @@
       <c r="C78" s="17"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>123</v>
@@ -3106,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
@@ -3122,10 +3114,10 @@
         <v>620</v>
       </c>
       <c r="D79" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>33</v>
@@ -3134,7 +3126,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
@@ -3144,16 +3136,16 @@
         <v>78</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C80" s="3">
         <v>506</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>22</v>
@@ -3162,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
@@ -3172,13 +3164,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C81" s="3">
         <v>414</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>29</v>
@@ -3190,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
@@ -3200,25 +3192,25 @@
         <v>80</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C82" s="3">
         <v>413</v>
       </c>
       <c r="D82" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="F82" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="G82" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="G82" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
@@ -3228,24 +3220,24 @@
         <v>81</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C83" s="17"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F83" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="G83" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="G83" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H83" s="6" t="s">
+      <c r="I83" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="I83" s="5" t="s">
-        <v>184</v>
       </c>
       <c r="J83" s="5"/>
     </row>
@@ -3253,7 +3245,7 @@
   <customSheetViews>
     <customSheetView guid="{77038CD4-2297-4E69-A928-9CF498AA6CA5}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:J83" xr:uid="{51EB7776-0972-4E67-9267-1849D967912E}"/>
+      <autoFilter ref="A1:J83" xr:uid="{C6FCA538-7978-46FB-9D11-C930C1C8FC64}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations count="1">

--- a/BICICLETERO 2026.xlsx
+++ b/BICICLETERO 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Concepto Style\Desktop\BICICLETERO 2.0\bicicletero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB26690-6F8F-41B4-BB93-FC0B101D6EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8537DB47-09D8-4BB9-8D33-8F6E5AB5CD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="105" windowWidth="15375" windowHeight="10185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -1843,7 +1843,7 @@
         <v>37</v>
       </c>
       <c r="G30" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>38</v>
@@ -3245,7 +3245,7 @@
   <customSheetViews>
     <customSheetView guid="{77038CD4-2297-4E69-A928-9CF498AA6CA5}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:J83" xr:uid="{C6FCA538-7978-46FB-9D11-C930C1C8FC64}"/>
+      <autoFilter ref="A1:J83" xr:uid="{EACC59EE-6D4A-4F7A-91A4-3C5A9AB88A40}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations count="1">

--- a/BICICLETERO 2026.xlsx
+++ b/BICICLETERO 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Concepto Style\Desktop\BICICLETERO 2.0\bicicletero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8537DB47-09D8-4BB9-8D33-8F6E5AB5CD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5DD739-DBDF-4057-A4C7-25955DF043B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="120" windowWidth="17265" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="205">
   <si>
     <t>ESPACIO</t>
   </si>
@@ -244,12 +244,6 @@
     <t>38.jpeg</t>
   </si>
   <si>
-    <t>UNLAND</t>
-  </si>
-  <si>
-    <t>CALIPSO</t>
-  </si>
-  <si>
     <t>39.jpeg</t>
   </si>
   <si>
@@ -307,12 +301,6 @@
     <t>44.jpeg</t>
   </si>
   <si>
-    <t>LAURA BARTOLOTTI</t>
-  </si>
-  <si>
-    <t>NEGRO CON CANASTO</t>
-  </si>
-  <si>
     <t>45.jpeg</t>
   </si>
   <si>
@@ -331,9 +319,6 @@
     <t>46.jpeg</t>
   </si>
   <si>
-    <t>CARLOS BELMAR</t>
-  </si>
-  <si>
     <t>47.jpeg</t>
   </si>
   <si>
@@ -385,9 +370,6 @@
     <t>52.jpeg</t>
   </si>
   <si>
-    <t>MARRON</t>
-  </si>
-  <si>
     <t>53.jpeg</t>
   </si>
   <si>
@@ -650,6 +632,15 @@
   </si>
   <si>
     <t>TREK 3700</t>
+  </si>
+  <si>
+    <t>MARIA JOSE VILLA</t>
+  </si>
+  <si>
+    <t>BRANTA 26</t>
+  </si>
+  <si>
+    <t>TURQUESA / AMARILLO</t>
   </si>
 </sst>
 </file>
@@ -706,7 +697,7 @@
       <name val="Roboto"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -727,26 +718,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6D9EEB"/>
-        <bgColor rgb="FF6D9EEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF9900"/>
-        <bgColor rgb="FFFF9900"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor theme="6"/>
       </patternFill>
     </fill>
   </fills>
@@ -827,7 +800,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -856,9 +829,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -874,20 +844,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1175,7 +1142,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J83"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -1230,11 +1197,9 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="G2" s="4"/>
       <c r="H2" s="6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
@@ -1254,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -1274,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -1294,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -1314,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
@@ -1334,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
@@ -1354,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
@@ -1374,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
@@ -1394,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -1414,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -1434,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -1454,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
@@ -1474,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
@@ -1494,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
@@ -1514,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
@@ -1534,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
@@ -1554,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
@@ -1574,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
@@ -1594,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
@@ -1614,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
@@ -1634,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
@@ -1674,11 +1639,12 @@
       <c r="B24" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C24" s="9"/>
       <c r="G24" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
@@ -2130,23 +2096,15 @@
       <c r="B41" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C41" s="10">
-        <v>716</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E41" s="3" t="s">
+      <c r="C41" s="9"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G41" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
@@ -2162,19 +2120,19 @@
         <v>707</v>
       </c>
       <c r="D42" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="G42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G42" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
@@ -2190,19 +2148,19 @@
         <v>104</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="G43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G43" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
@@ -2218,10 +2176,10 @@
         <v>515</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>33</v>
@@ -2230,7 +2188,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
@@ -2246,19 +2204,19 @@
         <v>306</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G45" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
@@ -2274,19 +2232,19 @@
         <v>318</v>
       </c>
       <c r="D46" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="G46" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G46" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
@@ -2298,26 +2256,18 @@
       <c r="B47" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C47" s="3">
-        <v>610</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="G47" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="14" t="s">
-        <v>95</v>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>91</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J47" s="5"/>
     </row>
@@ -2332,19 +2282,19 @@
         <v>513</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G48" s="15" t="b">
+        <v>95</v>
+      </c>
+      <c r="G48" s="14" t="b">
         <v>1</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
@@ -2356,23 +2306,15 @@
       <c r="B49" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C49" s="16">
-        <v>510</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="C49" s="9"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
       <c r="G49" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
@@ -2384,23 +2326,12 @@
       <c r="B50" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="3">
-        <v>502</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>105</v>
-      </c>
+      <c r="C50" s="9"/>
       <c r="G50" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
@@ -2412,13 +2343,23 @@
       <c r="B51" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
+      <c r="C51" s="3">
+        <v>502</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="G51" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
@@ -2434,10 +2375,10 @@
         <v>312</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>22</v>
@@ -2446,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
@@ -2458,23 +2399,23 @@
       <c r="B53" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="18">
         <v>608</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G53" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
@@ -2490,10 +2431,10 @@
         <v>408</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>22</v>
@@ -2502,7 +2443,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
@@ -2514,19 +2455,15 @@
       <c r="B55" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C55" s="17"/>
+      <c r="C55" s="9"/>
       <c r="D55" s="3"/>
-      <c r="E55" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
       <c r="G55" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
@@ -2538,23 +2475,23 @@
       <c r="B56" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C56" s="16">
+      <c r="C56" s="18">
         <v>505</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>122</v>
+        <v>203</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="G56" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
@@ -2566,7 +2503,7 @@
       <c r="B57" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C57" s="3"/>
+      <c r="C57" s="9"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -2574,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
@@ -2590,19 +2527,19 @@
         <v>320</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G58" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
@@ -2621,16 +2558,16 @@
         <v>32</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G59" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
@@ -2646,7 +2583,7 @@
         <v>514</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>51</v>
@@ -2658,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
@@ -2674,19 +2611,19 @@
         <v>204</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G61" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
@@ -2702,19 +2639,19 @@
         <v>207</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G62" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
@@ -2730,10 +2667,10 @@
         <v>418</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>14</v>
@@ -2742,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
@@ -2758,10 +2695,10 @@
         <v>506</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>33</v>
@@ -2770,7 +2707,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
@@ -2790,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
@@ -2806,19 +2743,19 @@
         <v>505</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G66" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
@@ -2833,20 +2770,20 @@
       <c r="C67" s="18">
         <v>713</v>
       </c>
-      <c r="D67" s="19" t="s">
-        <v>148</v>
+      <c r="D67" s="16" t="s">
+        <v>142</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G67" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
@@ -2858,11 +2795,11 @@
       <c r="B68" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C68" s="20">
+      <c r="C68" s="17">
         <v>216</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>65</v>
@@ -2874,7 +2811,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
@@ -2890,19 +2827,19 @@
         <v>517</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G69" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
@@ -2922,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
@@ -2942,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
@@ -2954,19 +2891,23 @@
       <c r="B72" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C72" s="17"/>
-      <c r="D72" s="3"/>
+      <c r="C72" s="15">
+        <v>420</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="E72" s="3" t="s">
         <v>65</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G72" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
@@ -2982,19 +2923,19 @@
         <v>309</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G73" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
@@ -3014,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
@@ -3034,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
@@ -3054,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
@@ -3074,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
@@ -3086,19 +3027,19 @@
       <c r="B78" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C78" s="17"/>
+      <c r="C78" s="15"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G78" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
@@ -3114,10 +3055,10 @@
         <v>620</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>33</v>
@@ -3126,7 +3067,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
@@ -3136,16 +3077,16 @@
         <v>78</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C80" s="3">
         <v>506</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>22</v>
@@ -3154,7 +3095,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
@@ -3164,13 +3105,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C81" s="3">
         <v>414</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>29</v>
@@ -3182,7 +3123,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
@@ -3192,25 +3133,25 @@
         <v>80</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C82" s="3">
         <v>413</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G82" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
@@ -3220,24 +3161,24 @@
         <v>81</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C83" s="17"/>
+        <v>165</v>
+      </c>
+      <c r="C83" s="15"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G83" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J83" s="5"/>
     </row>
@@ -3245,7 +3186,7 @@
   <customSheetViews>
     <customSheetView guid="{77038CD4-2297-4E69-A928-9CF498AA6CA5}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:J83" xr:uid="{EACC59EE-6D4A-4F7A-91A4-3C5A9AB88A40}"/>
+      <autoFilter ref="A1:J83" xr:uid="{BEA9CC79-8C7E-43F1-971A-4F14099F9372}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations count="1">

--- a/BICICLETERO 2026.xlsx
+++ b/BICICLETERO 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Concepto Style\Desktop\BICICLETERO 2.0\bicicletero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5DD739-DBDF-4057-A4C7-25955DF043B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2F32CE-E1F7-4D38-ACE0-EA1BE28DF8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="120" windowWidth="17265" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="45" windowWidth="17265" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="207">
   <si>
     <t>ESPACIO</t>
   </si>
@@ -641,13 +641,19 @@
   </si>
   <si>
     <t>TURQUESA / AMARILLO</t>
+  </si>
+  <si>
+    <t>TOTEM</t>
+  </si>
+  <si>
+    <t>AZUL LETRAS BLANCAS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -695,6 +701,20 @@
       <sz val="12"/>
       <color rgb="FF222222"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -800,7 +820,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -850,10 +870,14 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2399,7 +2423,7 @@
       <c r="B53" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="18">
+      <c r="C53" s="3">
         <v>608</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -2475,7 +2499,7 @@
       <c r="B56" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C56" s="18">
+      <c r="C56" s="3">
         <v>505</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -2739,7 +2763,7 @@
       <c r="B66" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C66" s="18">
+      <c r="C66" s="3">
         <v>505</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -2767,7 +2791,7 @@
       <c r="B67" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C67" s="18">
+      <c r="C67" s="3">
         <v>713</v>
       </c>
       <c r="D67" s="16" t="s">
@@ -3007,10 +3031,18 @@
       <c r="B77" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
+      <c r="C77" s="18">
+        <v>711</v>
+      </c>
+      <c r="D77" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="F77" s="20" t="s">
+        <v>206</v>
+      </c>
       <c r="G77" s="4" t="b">
         <v>0</v>
       </c>
@@ -3186,7 +3218,7 @@
   <customSheetViews>
     <customSheetView guid="{77038CD4-2297-4E69-A928-9CF498AA6CA5}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:J83" xr:uid="{BEA9CC79-8C7E-43F1-971A-4F14099F9372}"/>
+      <autoFilter ref="A1:J83" xr:uid="{FD79A8E1-6C63-4AC2-84D8-BDB712052004}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations count="1">
@@ -3258,9 +3290,9 @@
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd" r:id="rId61"/>
   <tableParts count="1">
-    <tablePart r:id="rId61"/>
+    <tablePart r:id="rId62"/>
   </tableParts>
 </worksheet>
 </file>
--- a/BICICLETERO 2026.xlsx
+++ b/BICICLETERO 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Concepto Style\Desktop\BICICLETERO 2.0\bicicletero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\BICICLETERO 3\bicicletero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2F32CE-E1F7-4D38-ACE0-EA1BE28DF8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA09F260-F3DB-44DD-B40E-65AFBC5C31C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="45" windowWidth="17265" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="204">
   <si>
     <t>ESPACIO</t>
   </si>
@@ -67,9 +67,6 @@
     <t>PABLO SILVA</t>
   </si>
   <si>
-    <t>OXFORD  29</t>
-  </si>
-  <si>
     <t>AZUL</t>
   </si>
   <si>
@@ -79,9 +76,6 @@
     <t>MELISSA GONZALEZ</t>
   </si>
   <si>
-    <t>TREEK</t>
-  </si>
-  <si>
     <t>PLATEADA</t>
   </si>
   <si>
@@ -91,9 +85,6 @@
     <t>DIEGO PINTO</t>
   </si>
   <si>
-    <t xml:space="preserve">TREEK </t>
-  </si>
-  <si>
     <t>NEGRA</t>
   </si>
   <si>
@@ -250,9 +241,6 @@
     <t>MICHAEL FIGUEROA</t>
   </si>
   <si>
-    <t>TREEK MARLIN 7</t>
-  </si>
-  <si>
     <t>AZUL MARINO</t>
   </si>
   <si>
@@ -304,9 +292,6 @@
     <t>45.jpeg</t>
   </si>
   <si>
-    <t>ESPACIO DE BICICLETERO OCUPADO POR OTRO RESIDENTE.</t>
-  </si>
-  <si>
     <t>ANDREA SCOFFIER</t>
   </si>
   <si>
@@ -325,9 +310,6 @@
     <t>GIANCARLO MUSSATO</t>
   </si>
   <si>
-    <t>TREEK MARLIN 5</t>
-  </si>
-  <si>
     <t>PLOMA</t>
   </si>
   <si>
@@ -559,9 +541,6 @@
     <t>81.jpeg</t>
   </si>
   <si>
-    <t>se mudo</t>
-  </si>
-  <si>
     <t>1.jpeg</t>
   </si>
   <si>
@@ -647,6 +626,18 @@
   </si>
   <si>
     <t>AZUL LETRAS BLANCAS</t>
+  </si>
+  <si>
+    <t>Espacio para visita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OXFORD  </t>
+  </si>
+  <si>
+    <t>TREK MARLIN 7</t>
+  </si>
+  <si>
+    <t>TREK MARLIN 5</t>
   </si>
 </sst>
 </file>
@@ -820,7 +811,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -872,9 +863,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1221,11 +1209,15 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="H2" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I2" s="5"/>
+        <v>171</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J2" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1243,9 +1235,11 @@
         <v>0</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="I3" s="5"/>
+        <v>172</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J3" s="5"/>
     </row>
     <row r="4" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1263,9 +1257,11 @@
         <v>0</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="I4" s="5"/>
+        <v>173</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J4" s="5"/>
     </row>
     <row r="5" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1283,9 +1279,11 @@
         <v>0</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="I5" s="5"/>
+        <v>174</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J5" s="5"/>
     </row>
     <row r="6" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1303,9 +1301,11 @@
         <v>0</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="I6" s="5"/>
+        <v>175</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J6" s="5"/>
     </row>
     <row r="7" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1323,9 +1323,11 @@
         <v>0</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="I7" s="5"/>
+        <v>176</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1343,9 +1345,11 @@
         <v>0</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="I8" s="5"/>
+        <v>177</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J8" s="5"/>
     </row>
     <row r="9" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1363,9 +1367,11 @@
         <v>0</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="I9" s="5"/>
+        <v>178</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J9" s="5"/>
     </row>
     <row r="10" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1383,9 +1389,11 @@
         <v>0</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="I10" s="5"/>
+        <v>179</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J10" s="5"/>
     </row>
     <row r="11" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1403,9 +1411,11 @@
         <v>0</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="I11" s="5"/>
+        <v>180</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1423,9 +1433,11 @@
         <v>0</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="I12" s="5"/>
+        <v>181</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J12" s="5"/>
     </row>
     <row r="13" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1443,9 +1455,11 @@
         <v>0</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="I13" s="5"/>
+        <v>182</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J13" s="5"/>
     </row>
     <row r="14" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1463,9 +1477,11 @@
         <v>0</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="I14" s="5"/>
+        <v>183</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J14" s="5"/>
     </row>
     <row r="15" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1483,9 +1499,11 @@
         <v>0</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="I15" s="5"/>
+        <v>184</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J15" s="5"/>
     </row>
     <row r="16" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1503,9 +1521,11 @@
         <v>0</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="I16" s="5"/>
+        <v>185</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J16" s="5"/>
     </row>
     <row r="17" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1523,9 +1543,11 @@
         <v>0</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="I17" s="5"/>
+        <v>186</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J17" s="5"/>
     </row>
     <row r="18" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1543,9 +1565,11 @@
         <v>0</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="I18" s="5"/>
+        <v>187</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J18" s="5"/>
     </row>
     <row r="19" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1563,9 +1587,11 @@
         <v>0</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I19" s="5"/>
+        <v>188</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J19" s="5"/>
     </row>
     <row r="20" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1583,9 +1609,11 @@
         <v>0</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="I20" s="5"/>
+        <v>189</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J20" s="5"/>
     </row>
     <row r="21" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1603,9 +1631,11 @@
         <v>0</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="I21" s="5"/>
+        <v>190</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J21" s="5"/>
     </row>
     <row r="22" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1623,9 +1653,11 @@
         <v>0</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="I22" s="5"/>
+        <v>191</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="J22" s="5"/>
     </row>
     <row r="23" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1642,16 +1674,16 @@
         <v>12</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="G23" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
@@ -1668,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
@@ -1684,19 +1716,19 @@
         <v>715</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="G25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
@@ -1712,19 +1744,19 @@
         <v>709</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
@@ -1740,19 +1772,19 @@
         <v>203</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
@@ -1768,19 +1800,19 @@
         <v>301</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G28" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
@@ -1796,19 +1828,19 @@
         <v>704</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G29" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
@@ -1824,19 +1856,19 @@
         <v>215</v>
       </c>
       <c r="D30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G30" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
@@ -1852,19 +1884,19 @@
         <v>406</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G31" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
@@ -1880,19 +1912,19 @@
         <v>603</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G32" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
@@ -1908,19 +1940,19 @@
         <v>508</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G33" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
@@ -1936,19 +1968,19 @@
         <v>716</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G34" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
@@ -1964,19 +1996,19 @@
         <v>519</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G35" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
@@ -1992,29 +2024,29 @@
         <v>501</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G36" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
     </row>
     <row r="37" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="3"/>
@@ -2024,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
@@ -2034,25 +2066,25 @@
         <v>36</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C38" s="3">
         <v>103</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G38" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
@@ -2062,25 +2094,25 @@
         <v>37</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C39" s="3">
         <v>616</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G39" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
@@ -2090,25 +2122,25 @@
         <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C40" s="3">
         <v>305</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G40" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
@@ -2118,7 +2150,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="3"/>
@@ -2128,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
@@ -2138,25 +2170,25 @@
         <v>40</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C42" s="3">
         <v>707</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>74</v>
+        <v>202</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G42" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
@@ -2166,25 +2198,25 @@
         <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C43" s="3">
         <v>104</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G43" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
@@ -2194,25 +2226,25 @@
         <v>42</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C44" s="3">
         <v>515</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G44" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
@@ -2222,25 +2254,25 @@
         <v>43</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C45" s="3">
         <v>306</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G45" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
@@ -2250,25 +2282,25 @@
         <v>44</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C46" s="3">
         <v>318</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G46" s="10" t="b">
         <v>1</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
@@ -2278,7 +2310,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
@@ -2288,11 +2320,9 @@
         <v>0</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="I47" s="5" t="s">
-        <v>92</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="I47" s="5"/>
       <c r="J47" s="5"/>
     </row>
     <row r="48" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2300,25 +2330,25 @@
         <v>46</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C48" s="3">
         <v>513</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G48" s="14" t="b">
         <v>1</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
@@ -2328,7 +2358,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="3"/>
@@ -2338,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
@@ -2348,14 +2378,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C50" s="9"/>
       <c r="G50" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
@@ -2365,25 +2395,25 @@
         <v>49</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C51" s="3">
         <v>502</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>99</v>
+        <v>203</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G51" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
@@ -2393,25 +2423,25 @@
         <v>50</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C52" s="3">
         <v>312</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G52" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
@@ -2421,25 +2451,25 @@
         <v>51</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C53" s="3">
         <v>608</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G53" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
@@ -2449,25 +2479,25 @@
         <v>52</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C54" s="3">
         <v>408</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G54" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
@@ -2477,7 +2507,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="3"/>
@@ -2487,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
@@ -2497,25 +2527,25 @@
         <v>54</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C56" s="3">
         <v>505</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="G56" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
@@ -2525,7 +2555,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="3"/>
@@ -2535,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
@@ -2545,25 +2575,25 @@
         <v>56</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C58" s="3">
         <v>320</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G58" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
@@ -2573,25 +2603,25 @@
         <v>57</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C59" s="3">
         <v>704</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G59" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
@@ -2601,25 +2631,25 @@
         <v>58</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C60" s="3">
         <v>514</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G60" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
@@ -2629,25 +2659,25 @@
         <v>59</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C61" s="3">
         <v>204</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G61" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
@@ -2657,25 +2687,25 @@
         <v>60</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C62" s="3">
         <v>207</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="G62" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
@@ -2685,25 +2715,25 @@
         <v>61</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C63" s="3">
         <v>418</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G63" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
@@ -2713,25 +2743,25 @@
         <v>62</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C64" s="3">
         <v>506</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G64" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
@@ -2741,7 +2771,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="3"/>
@@ -2751,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
@@ -2761,25 +2791,25 @@
         <v>64</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C66" s="3">
         <v>505</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G66" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
@@ -2789,25 +2819,25 @@
         <v>65</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C67" s="3">
         <v>713</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G67" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
@@ -2817,25 +2847,25 @@
         <v>66</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C68" s="17">
         <v>216</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G68" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
@@ -2845,25 +2875,25 @@
         <v>67</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C69" s="3">
         <v>517</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G69" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
@@ -2873,7 +2903,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="3"/>
@@ -2883,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
@@ -2893,7 +2923,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="3"/>
@@ -2903,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
@@ -2913,25 +2943,25 @@
         <v>70</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C72" s="15">
         <v>420</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G72" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
@@ -2941,25 +2971,25 @@
         <v>71</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C73" s="3">
         <v>309</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G73" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
@@ -2969,7 +2999,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="3"/>
@@ -2979,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
@@ -2989,7 +3019,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="3"/>
@@ -2999,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
@@ -3009,7 +3039,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="3"/>
@@ -3019,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
@@ -3029,25 +3059,25 @@
         <v>75</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C77" s="18">
+        <v>55</v>
+      </c>
+      <c r="C77" s="3">
         <v>711</v>
       </c>
-      <c r="D77" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="E77" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="F77" s="20" t="s">
-        <v>206</v>
+      <c r="D77" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>199</v>
       </c>
       <c r="G77" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
@@ -3057,21 +3087,21 @@
         <v>76</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C78" s="15"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G78" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
@@ -3081,25 +3111,25 @@
         <v>77</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C79" s="3">
         <v>620</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G79" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
@@ -3109,25 +3139,25 @@
         <v>78</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C80" s="3">
         <v>506</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G80" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
@@ -3137,25 +3167,25 @@
         <v>79</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C81" s="3">
         <v>414</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G81" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
@@ -3165,25 +3195,25 @@
         <v>80</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C82" s="3">
         <v>413</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G82" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
@@ -3193,32 +3223,30 @@
         <v>81</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G83" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="I83" s="5" t="s">
-        <v>177</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="I83" s="5"/>
       <c r="J83" s="5"/>
     </row>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{77038CD4-2297-4E69-A928-9CF498AA6CA5}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:J83" xr:uid="{FD79A8E1-6C63-4AC2-84D8-BDB712052004}"/>
+      <autoFilter ref="A1:J83" xr:uid="{C93C8516-27DB-4F0F-A831-700082BA7855}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations count="1">

--- a/BICICLETERO 2026.xlsx
+++ b/BICICLETERO 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\BICICLETERO 3\bicicletero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA09F260-F3DB-44DD-B40E-65AFBC5C31C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA317C96-82B0-4D56-A392-9924C72DEB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="216">
   <si>
     <t>ESPACIO</t>
   </si>
@@ -472,12 +472,6 @@
     <t>70.jpeg</t>
   </si>
   <si>
-    <t>MARCCELO MUÑOZ</t>
-  </si>
-  <si>
-    <t>NEGRO DETALE ROJO/AZUL</t>
-  </si>
-  <si>
     <t>71.jpeg</t>
   </si>
   <si>
@@ -638,6 +632,48 @@
   </si>
   <si>
     <t>TREK MARLIN 5</t>
+  </si>
+  <si>
+    <t>FRANCISCA ASTUDILLO</t>
+  </si>
+  <si>
+    <t>CAFÉ</t>
+  </si>
+  <si>
+    <t>KAREN GONZALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OXFORD </t>
+  </si>
+  <si>
+    <t>CALIPSO</t>
+  </si>
+  <si>
+    <t>BLANCO</t>
+  </si>
+  <si>
+    <t>FUCSIA</t>
+  </si>
+  <si>
+    <t>GRIS LETRA NARANJA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE PALACIOS</t>
+  </si>
+  <si>
+    <t>NARANJA / CELESTE</t>
+  </si>
+  <si>
+    <t>NEGRO / ROJO / AZUL</t>
+  </si>
+  <si>
+    <t>MARCELO MUÑOZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TREK </t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
   </si>
 </sst>
 </file>
@@ -708,7 +744,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -730,6 +766,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
@@ -811,7 +865,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -846,9 +900,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -866,6 +917,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1159,7 +1219,7 @@
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" customWidth="1"/>
-    <col min="4" max="4" width="25.85546875" customWidth="1"/>
+    <col min="4" max="4" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.85546875" customWidth="1"/>
     <col min="6" max="6" width="33.42578125" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -1213,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J2" s="5"/>
     </row>
@@ -1235,10 +1295,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J3" s="5"/>
     </row>
@@ -1257,10 +1317,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J4" s="5"/>
     </row>
@@ -1279,10 +1339,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J5" s="5"/>
     </row>
@@ -1301,10 +1361,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J6" s="5"/>
     </row>
@@ -1323,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J7" s="5"/>
     </row>
@@ -1345,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J8" s="5"/>
     </row>
@@ -1367,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J9" s="5"/>
     </row>
@@ -1389,10 +1449,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J10" s="5"/>
     </row>
@@ -1411,10 +1471,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J11" s="5"/>
     </row>
@@ -1433,10 +1493,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J12" s="5"/>
     </row>
@@ -1455,10 +1515,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J13" s="5"/>
     </row>
@@ -1477,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J14" s="5"/>
     </row>
@@ -1499,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J15" s="5"/>
     </row>
@@ -1521,10 +1581,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J16" s="5"/>
     </row>
@@ -1543,10 +1603,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J17" s="5"/>
     </row>
@@ -1565,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J18" s="5"/>
     </row>
@@ -1587,10 +1647,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J19" s="5"/>
     </row>
@@ -1609,10 +1669,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J20" s="5"/>
     </row>
@@ -1631,10 +1691,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J21" s="5"/>
     </row>
@@ -1653,10 +1713,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J22" s="5"/>
     </row>
@@ -1674,7 +1734,7 @@
         <v>12</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>111</v>
@@ -1695,12 +1755,23 @@
       <c r="B24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="9"/>
+      <c r="C24" s="19">
+        <v>502</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G24" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
@@ -2048,12 +2119,20 @@
       <c r="B37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
+      <c r="C37" s="9">
+        <v>312</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="G37" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>56</v>
@@ -2152,12 +2231,20 @@
       <c r="B41" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
+      <c r="C41" s="3">
+        <v>707</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>207</v>
+      </c>
       <c r="G41" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>69</v>
@@ -2179,7 +2266,7 @@
         <v>70</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>71</v>
@@ -2312,14 +2399,22 @@
       <c r="B47" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="13" t="s">
+      <c r="C47" s="3">
+        <v>216</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" s="12" t="s">
         <v>87</v>
       </c>
       <c r="I47" s="5"/>
@@ -2344,7 +2439,7 @@
       <c r="F48" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G48" s="14" t="b">
+      <c r="G48" s="13" t="b">
         <v>1</v>
       </c>
       <c r="H48" s="6" t="s">
@@ -2360,12 +2455,20 @@
       <c r="B49" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C49" s="9"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
+      <c r="C49" s="9">
+        <v>413</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="G49" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>92</v>
@@ -2380,7 +2483,7 @@
       <c r="B50" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="9"/>
+      <c r="F50" s="3"/>
       <c r="G50" s="4" t="b">
         <v>0</v>
       </c>
@@ -2404,7 +2507,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>94</v>
@@ -2509,12 +2612,20 @@
       <c r="B55" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
+      <c r="C55" s="9">
+        <v>501</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>209</v>
+      </c>
       <c r="G55" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>108</v>
@@ -2536,10 +2647,10 @@
         <v>109</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G56" s="4" t="b">
         <v>1</v>
@@ -2557,12 +2668,20 @@
       <c r="B57" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
+      <c r="C57" s="9">
+        <v>616</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="G57" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>113</v>
@@ -2724,7 +2843,7 @@
         <v>128</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>13</v>
@@ -2773,12 +2892,20 @@
       <c r="B65" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C65" s="9"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
+      <c r="C65" s="9">
+        <v>418</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="G65" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>133</v>
@@ -2824,7 +2951,7 @@
       <c r="C67" s="3">
         <v>713</v>
       </c>
-      <c r="D67" s="16" t="s">
+      <c r="D67" s="15" t="s">
         <v>136</v>
       </c>
       <c r="E67" s="3" t="s">
@@ -2849,7 +2976,7 @@
       <c r="B68" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C68" s="17">
+      <c r="C68" s="16">
         <v>216</v>
       </c>
       <c r="D68" s="7" t="s">
@@ -2905,12 +3032,20 @@
       <c r="B70" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C70" s="9"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
+      <c r="C70" s="9">
+        <v>318</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G70" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>144</v>
@@ -2925,12 +3060,20 @@
       <c r="B71" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C71" s="9"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
+      <c r="C71" s="9">
+        <v>204</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="G71" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>145</v>
@@ -2945,11 +3088,11 @@
       <c r="B72" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C72" s="15">
+      <c r="C72" s="21">
         <v>420</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>62</v>
@@ -2958,7 +3101,7 @@
         <v>146</v>
       </c>
       <c r="G72" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>147</v>
@@ -2977,19 +3120,19 @@
         <v>309</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>148</v>
+        <v>213</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="G73" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
@@ -3001,15 +3144,23 @@
       <c r="B74" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C74" s="9"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
+      <c r="C74" s="9">
+        <v>309</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>207</v>
+      </c>
       <c r="G74" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
@@ -3021,15 +3172,23 @@
       <c r="B75" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
+      <c r="C75" s="9">
+        <v>514</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G75" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
@@ -3049,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
@@ -3064,20 +3223,20 @@
       <c r="C77" s="3">
         <v>711</v>
       </c>
-      <c r="D77" s="18" t="s">
+      <c r="D77" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E77" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="F77" s="19" t="s">
-        <v>199</v>
+      <c r="E77" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F77" s="18" t="s">
+        <v>197</v>
       </c>
       <c r="G77" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
@@ -3089,19 +3248,23 @@
       <c r="B78" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C78" s="15"/>
-      <c r="D78" s="3"/>
+      <c r="C78" s="20">
+        <v>716</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="E78" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>111</v>
       </c>
       <c r="G78" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
@@ -3117,10 +3280,10 @@
         <v>620</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>30</v>
@@ -3129,7 +3292,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
@@ -3139,7 +3302,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C80" s="3">
         <v>506</v>
@@ -3148,7 +3311,7 @@
         <v>130</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>19</v>
@@ -3157,7 +3320,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
@@ -3167,13 +3330,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C81" s="3">
         <v>414</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>26</v>
@@ -3185,7 +3348,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
@@ -3195,25 +3358,25 @@
         <v>80</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C82" s="3">
         <v>413</v>
       </c>
       <c r="D82" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F82" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="G82" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G82" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
@@ -3223,21 +3386,21 @@
         <v>81</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C83" s="15"/>
+        <v>157</v>
+      </c>
+      <c r="C83" s="14"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G83" s="4" t="b">
         <v>0</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
@@ -3246,7 +3409,7 @@
   <customSheetViews>
     <customSheetView guid="{77038CD4-2297-4E69-A928-9CF498AA6CA5}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:J83" xr:uid="{C93C8516-27DB-4F0F-A831-700082BA7855}"/>
+      <autoFilter ref="A1:J83" xr:uid="{DA9FE309-8BAF-4212-AE89-7E43A301FE35}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations count="1">

--- a/BICICLETERO 2026.xlsx
+++ b/BICICLETERO 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\BICICLETERO 3\bicicletero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Concepto Style\Desktop\BICICLETERO 2.0\bicicletero\bicicletero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA317C96-82B0-4D56-A392-9924C72DEB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0454A32-836A-4B7A-8742-5164FBEFE2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="219">
   <si>
     <t>ESPACIO</t>
   </si>
@@ -674,13 +674,22 @@
   </si>
   <si>
     <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>ROSADO METALICO</t>
+  </si>
+  <si>
+    <t>ROJA LETRAS BLANCAS</t>
+  </si>
+  <si>
+    <t>PROCESO DE RETIRO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -713,11 +722,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF434343"/>
-      <name val="Roboto"/>
-    </font>
-    <font>
       <u/>
       <sz val="10"/>
       <color theme="1"/>
@@ -743,8 +747,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -759,12 +774,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
       </patternFill>
@@ -773,18 +782,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FF00FF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -865,7 +862,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -885,14 +882,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -900,32 +891,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1755,7 +1746,7 @@
       <c r="B24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="16">
         <v>502</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -2041,10 +2032,10 @@
       <c r="D34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="18" t="s">
         <v>45</v>
       </c>
       <c r="G34" s="4" t="b">
@@ -2085,7 +2076,7 @@
       <c r="J35" s="5"/>
     </row>
     <row r="36" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="8">
+      <c r="A36" s="7">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -2113,26 +2104,14 @@
       <c r="J36" s="5"/>
     </row>
     <row r="37" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="9">
-        <v>312</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="G37" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>56</v>
@@ -2383,7 +2362,7 @@
       <c r="F46" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G46" s="10" t="b">
+      <c r="G46" s="8" t="b">
         <v>1</v>
       </c>
       <c r="H46" s="6" t="s">
@@ -2408,13 +2387,13 @@
       <c r="E47" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="9" t="s">
         <v>111</v>
       </c>
       <c r="G47" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H47" s="12" t="s">
+      <c r="H47" s="10" t="s">
         <v>87</v>
       </c>
       <c r="I47" s="5"/>
@@ -2439,7 +2418,7 @@
       <c r="F48" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G48" s="13" t="b">
+      <c r="G48" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H48" s="6" t="s">
@@ -2455,7 +2434,7 @@
       <c r="B49" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="3">
         <v>413</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -2483,9 +2462,20 @@
       <c r="B50" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F50" s="3"/>
+      <c r="C50" s="3">
+        <v>312</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="G50" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>95</v>
@@ -2612,7 +2602,7 @@
       <c r="B55" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C55" s="3">
         <v>501</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -2668,7 +2658,7 @@
       <c r="B57" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C57" s="9">
+      <c r="C57" s="3">
         <v>616</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -2892,7 +2882,7 @@
       <c r="B65" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C65" s="9">
+      <c r="C65" s="3">
         <v>418</v>
       </c>
       <c r="D65" s="3" t="s">
@@ -2951,7 +2941,7 @@
       <c r="C67" s="3">
         <v>713</v>
       </c>
-      <c r="D67" s="15" t="s">
+      <c r="D67" s="13" t="s">
         <v>136</v>
       </c>
       <c r="E67" s="3" t="s">
@@ -2976,16 +2966,16 @@
       <c r="B68" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C68" s="16">
+      <c r="C68" s="17">
         <v>216</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E68" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="F68" s="18" t="s">
         <v>30</v>
       </c>
       <c r="G68" s="4" t="b">
@@ -3032,7 +3022,7 @@
       <c r="B70" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C70" s="9">
+      <c r="C70" s="3">
         <v>318</v>
       </c>
       <c r="D70" s="3" t="s">
@@ -3042,7 +3032,7 @@
         <v>62</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G70" s="4" t="b">
         <v>1</v>
@@ -3060,7 +3050,7 @@
       <c r="B71" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C71" s="9">
+      <c r="C71" s="3">
         <v>204</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -3088,7 +3078,7 @@
       <c r="B72" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C72" s="21">
+      <c r="C72" s="3">
         <v>420</v>
       </c>
       <c r="D72" s="3" t="s">
@@ -3144,7 +3134,7 @@
       <c r="B74" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C74" s="9">
+      <c r="C74" s="3">
         <v>309</v>
       </c>
       <c r="D74" s="3" t="s">
@@ -3172,7 +3162,7 @@
       <c r="B75" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C75" s="9">
+      <c r="C75" s="3">
         <v>514</v>
       </c>
       <c r="D75" s="3" t="s">
@@ -3200,17 +3190,25 @@
       <c r="B76" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C76" s="9"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
+      <c r="C76" s="3">
+        <v>301</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="G76" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I76" s="5"/>
+      <c r="I76" s="19"/>
       <c r="J76" s="5"/>
     </row>
     <row r="77" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3223,13 +3221,13 @@
       <c r="C77" s="3">
         <v>711</v>
       </c>
-      <c r="D77" s="17" t="s">
+      <c r="D77" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E77" s="18" t="s">
+      <c r="E77" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="F77" s="18" t="s">
+      <c r="F77" s="15" t="s">
         <v>197</v>
       </c>
       <c r="G77" s="4" t="b">
@@ -3248,7 +3246,7 @@
       <c r="B78" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C78" s="20">
+      <c r="C78" s="3">
         <v>716</v>
       </c>
       <c r="D78" s="3" t="s">
@@ -3388,8 +3386,10 @@
       <c r="B83" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C83" s="14"/>
-      <c r="D83" s="3"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="3" t="s">
+        <v>218</v>
+      </c>
       <c r="E83" s="3" t="s">
         <v>166</v>
       </c>
@@ -3409,7 +3409,7 @@
   <customSheetViews>
     <customSheetView guid="{77038CD4-2297-4E69-A928-9CF498AA6CA5}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:J83" xr:uid="{DA9FE309-8BAF-4212-AE89-7E43A301FE35}"/>
+      <autoFilter ref="A1:J83" xr:uid="{3B9947BC-0D1B-474D-8EE1-817DB6854C8A}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations count="1">
